--- a/AAII_Financials/Quarterly/TOWN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TOWN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
   <si>
     <t>TOWN</t>
   </si>
@@ -656,306 +656,313 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AQ102"/>
+  <dimension ref="A5:AR102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AQ7" s="2">
+      <c r="AR7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>443600</v>
+      </c>
+      <c r="E8" s="3">
         <v>246100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>220700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200400</v>
       </c>
-      <c r="G8" s="3">
-        <v>201000</v>
-      </c>
       <c r="H8" s="3">
+        <v>203700</v>
+      </c>
+      <c r="I8" s="3">
         <v>180700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>175100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>175600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>175100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>168000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>153100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>171900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>178000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>172500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>151900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>137500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>120100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>108400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>109500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>109800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>111800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>112300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>116000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>115500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>114500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>114100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>116500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>119600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>117900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>113800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>114300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>110400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>105300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>91900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>78500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>77900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>78700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>70100</v>
-      </c>
-      <c r="AO8" s="3">
-        <v>71800</v>
       </c>
       <c r="AP8" s="3">
         <v>71800</v>
       </c>
       <c r="AQ8" s="3">
+        <v>71800</v>
+      </c>
+      <c r="AR8" s="3">
         <v>56200</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1079,53 +1086,56 @@
       <c r="AQ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AR9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>443600</v>
+      </c>
+      <c r="E10" s="3">
         <v>246100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>220700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200400</v>
       </c>
-      <c r="G10" s="3">
-        <v>201000</v>
-      </c>
       <c r="H10" s="3">
+        <v>203700</v>
+      </c>
+      <c r="I10" s="3">
         <v>180700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>175100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>175600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>175100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>168000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>153100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>171900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>178000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>172500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1204,8 +1214,11 @@
       <c r="AQ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AR10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1249,8 +1262,9 @@
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
       <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1374,8 +1388,11 @@
       <c r="AQ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AR12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1499,53 +1516,56 @@
       <c r="AQ13" s="3">
         <v>0</v>
       </c>
+      <c r="AR13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E14" s="3">
         <v>31700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>18300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>17800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>18700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1624,121 +1644,124 @@
       <c r="AQ14" s="3">
         <v>0</v>
       </c>
+      <c r="AR14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E15" s="3">
         <v>13200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8600</v>
-      </c>
-      <c r="I15" s="3">
-        <v>8700</v>
       </c>
       <c r="J15" s="3">
         <v>8700</v>
       </c>
       <c r="K15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="L15" s="3">
         <v>9000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8500</v>
-      </c>
-      <c r="N15" s="3">
-        <v>8700</v>
       </c>
       <c r="O15" s="3">
         <v>8700</v>
       </c>
       <c r="P15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>8400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-2500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-2600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-2700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-2800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-2900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-2800</v>
-      </c>
-      <c r="W15" s="3">
-        <v>-2700</v>
       </c>
       <c r="X15" s="3">
         <v>-2700</v>
       </c>
       <c r="Y15" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-2800</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>-2900</v>
       </c>
       <c r="AA15" s="3">
         <v>-2900</v>
       </c>
       <c r="AB15" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="AC15" s="3">
         <v>-3000</v>
       </c>
       <c r="AD15" s="3">
-        <v>-3100</v>
+        <v>-3000</v>
       </c>
       <c r="AE15" s="3">
         <v>-3100</v>
       </c>
       <c r="AF15" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AG15" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>-3000</v>
       </c>
       <c r="AI15" s="3">
         <v>-3000</v>
       </c>
       <c r="AJ15" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AK15" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>-2000</v>
       </c>
       <c r="AM15" s="3">
         <v>-2000</v>
       </c>
       <c r="AN15" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="AO15" s="3">
         <v>-1900</v>
@@ -1747,10 +1770,13 @@
         <v>-1900</v>
       </c>
       <c r="AQ15" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AR15" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1791,258 +1817,265 @@
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
       <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
     </row>
-    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>172900</v>
+      </c>
+      <c r="E17" s="3">
         <v>157900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>143000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>131500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>127900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>127100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>124100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>123300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>120700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>121800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>118400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>113500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>118600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>114900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>29200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>20300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>26000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>30100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>30000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>30900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>27800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>27400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>22900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>21500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>17500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>13700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>12600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>10700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>12300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>11500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>10900</v>
       </c>
-      <c r="AQ17" s="3">
+      <c r="AR17" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>270800</v>
+      </c>
+      <c r="E18" s="3">
         <v>88200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>77700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>68900</v>
       </c>
-      <c r="G18" s="3">
-        <v>73100</v>
-      </c>
       <c r="H18" s="3">
+        <v>75700</v>
+      </c>
+      <c r="I18" s="3">
         <v>53600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>51000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>52300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>54500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>46200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>58300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>59400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>57600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>122700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>120100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>109200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>100700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>101900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>102000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>111200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>104000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>100400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>95200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>90400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>88100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>86400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>89600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>87000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>86000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>86900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>87500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>83800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>74400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>64800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>65300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>68000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>57800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>60300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>60900</v>
       </c>
-      <c r="AQ18" s="3">
+      <c r="AR18" s="3">
         <v>45600</v>
       </c>
     </row>
-    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2086,258 +2119,265 @@
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
       <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
     </row>
-    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E20" s="3">
         <v>6300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>3100</v>
       </c>
       <c r="J20" s="3">
         <v>3100</v>
       </c>
       <c r="K20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L20" s="3">
         <v>3300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>3600</v>
       </c>
       <c r="O20" s="3">
         <v>3600</v>
       </c>
       <c r="P20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q20" s="3">
         <v>3500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-64600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-56800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-51000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-43200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-50800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-34400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-39200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-14800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-36100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-36700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-45700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-54300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-42600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-42500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-41900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-45700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-40100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-39100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-39000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-42400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-30200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-24800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-27800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-25400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-33300</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-24100</v>
       </c>
-      <c r="AQ20" s="3">
+      <c r="AR20" s="3">
         <v>-35400</v>
       </c>
     </row>
-    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>277600</v>
+      </c>
+      <c r="E21" s="3">
         <v>95100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>83900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>74800</v>
       </c>
-      <c r="G21" s="3">
-        <v>78800</v>
-      </c>
       <c r="H21" s="3">
+        <v>81400</v>
+      </c>
+      <c r="I21" s="3">
         <v>59200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>56600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>57900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>60200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>51700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>39800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>63400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>64400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>62500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>65300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>70400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>65300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>64800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>58400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>74800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>79000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>96400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>71600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>65900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>51900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>41100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>51100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>54400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>52500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>47700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>54100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>55700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>52000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>38900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>40700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>46600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>46500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>38300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>33000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>42700</v>
       </c>
-      <c r="AQ21" s="3">
+      <c r="AR21" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2380,8 +2420,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2461,258 +2501,267 @@
       <c r="AQ22" s="3">
         <v>0</v>
       </c>
+      <c r="AR22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>253700</v>
+      </c>
+      <c r="E23" s="3">
         <v>50200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>54100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>46700</v>
       </c>
-      <c r="G23" s="3">
-        <v>50400</v>
-      </c>
       <c r="H23" s="3">
+        <v>53000</v>
+      </c>
+      <c r="I23" s="3">
         <v>50100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>47600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>48700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>51200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>42400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>54200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>52800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>48100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>58100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>63300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>58200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>57500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>51100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>67600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>72000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>89200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>64300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>58600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>44700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>33800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>43700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>47100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>45200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>40300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>46800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>48400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>44800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>32000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>34600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>40500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>40200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>32400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>27000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>36800</v>
       </c>
-      <c r="AQ23" s="3">
+      <c r="AR23" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>60100</v>
+      </c>
+      <c r="E24" s="3">
         <v>9100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7400</v>
       </c>
-      <c r="G24" s="3">
-        <v>11100</v>
-      </c>
       <c r="H24" s="3">
+        <v>11700</v>
+      </c>
+      <c r="I24" s="3">
         <v>6100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2700</v>
-      </c>
-      <c r="N24" s="3">
-        <v>9400</v>
       </c>
       <c r="O24" s="3">
         <v>9400</v>
       </c>
       <c r="P24" s="3">
+        <v>9400</v>
+      </c>
+      <c r="Q24" s="3">
         <v>9600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>11200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>14800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>14000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>10400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>8900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>8200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>9700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>9200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>8600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>6100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>11200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>11900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>12200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>9400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>7200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>11000</v>
       </c>
-      <c r="AQ24" s="3">
+      <c r="AR24" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2836,258 +2885,267 @@
       <c r="AQ25" s="3">
         <v>0</v>
       </c>
+      <c r="AR25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>193600</v>
+      </c>
+      <c r="E26" s="3">
         <v>41100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>41300</v>
-      </c>
-      <c r="F26" s="3">
-        <v>39300</v>
       </c>
       <c r="G26" s="3">
         <v>39300</v>
       </c>
       <c r="H26" s="3">
+        <v>41300</v>
+      </c>
+      <c r="I26" s="3">
         <v>44000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>41100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>43100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>43000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>35100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>44700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>43400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>38500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>46500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>50700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>47100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>46300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>41700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>52700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>58000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>72600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>53900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>50700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>37200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>27600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>35900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>39400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>36200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>32100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>37100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>39300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>36100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>25900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>23400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>28600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>27900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>23000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>19800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>25800</v>
       </c>
-      <c r="AQ26" s="3">
+      <c r="AR26" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>193200</v>
+      </c>
+      <c r="E27" s="3">
         <v>41000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>41100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>39000</v>
       </c>
-      <c r="G27" s="3">
-        <v>38800</v>
-      </c>
       <c r="H27" s="3">
+        <v>40900</v>
+      </c>
+      <c r="I27" s="3">
         <v>43700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>40900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>42900</v>
       </c>
       <c r="K27" s="3">
         <v>42900</v>
       </c>
       <c r="L27" s="3">
+        <v>42900</v>
+      </c>
+      <c r="M27" s="3">
         <v>34700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>44900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>41700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>38300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>46700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>50200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>46500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>45600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>40200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>50400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>55800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>69000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>50100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>34500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>34600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>26400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>35100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>37700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>34600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>31400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>36700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>38300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>34800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>24700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>22400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>27200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>26200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>22000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>19000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>24200</v>
       </c>
-      <c r="AQ27" s="3">
+      <c r="AR27" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3211,8 +3269,11 @@
       <c r="AQ28" s="3">
         <v>0</v>
       </c>
+      <c r="AR28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3282,8 +3343,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -3303,24 +3364,24 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-700</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-10100</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3336,8 +3397,11 @@
       <c r="AQ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AR29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3461,8 +3525,11 @@
       <c r="AQ30" s="3">
         <v>0</v>
       </c>
+      <c r="AR30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3586,258 +3653,267 @@
       <c r="AQ31" s="3">
         <v>0</v>
       </c>
+      <c r="AR31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-3100</v>
       </c>
       <c r="J32" s="3">
         <v>-3100</v>
       </c>
       <c r="K32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="L32" s="3">
         <v>-3300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-3600</v>
       </c>
       <c r="O32" s="3">
         <v>-3600</v>
       </c>
       <c r="P32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>64600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>56800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>51000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>43200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>50800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>34400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>39200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>14800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>36100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>36700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>45700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>54300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>42600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>42500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>41900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>45700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>40100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>39100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>42400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>30200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>24800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>27800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>25400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>33300</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>24100</v>
       </c>
-      <c r="AQ32" s="3">
+      <c r="AR32" s="3">
         <v>35400</v>
       </c>
     </row>
-    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>193200</v>
+      </c>
+      <c r="E33" s="3">
         <v>41000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>41100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>39000</v>
       </c>
-      <c r="G33" s="3">
-        <v>38800</v>
-      </c>
       <c r="H33" s="3">
+        <v>40900</v>
+      </c>
+      <c r="I33" s="3">
         <v>43700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>40900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>42900</v>
       </c>
       <c r="K33" s="3">
         <v>42900</v>
       </c>
       <c r="L33" s="3">
+        <v>42900</v>
+      </c>
+      <c r="M33" s="3">
         <v>34700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>44900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>41700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>38300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>46700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>50200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>46500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>45600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>40200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>50400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>55800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>69000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>50100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>34500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>34600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>26400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>35100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>37700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>34600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>31400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>36000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>38300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>34800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>24700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>12300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>27200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>26200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>22000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>19000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>24200</v>
       </c>
-      <c r="AQ33" s="3">
+      <c r="AR33" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3961,263 +4037,272 @@
       <c r="AQ34" s="3">
         <v>0</v>
       </c>
+      <c r="AR34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>193200</v>
+      </c>
+      <c r="E35" s="3">
         <v>41000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>41100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>39000</v>
       </c>
-      <c r="G35" s="3">
-        <v>38800</v>
-      </c>
       <c r="H35" s="3">
+        <v>40900</v>
+      </c>
+      <c r="I35" s="3">
         <v>43700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>40900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>42900</v>
       </c>
       <c r="K35" s="3">
         <v>42900</v>
       </c>
       <c r="L35" s="3">
+        <v>42900</v>
+      </c>
+      <c r="M35" s="3">
         <v>34700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>44900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>41700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>38300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>46700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>50200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>46500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>45600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>40200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>50400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>55800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>69000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>50100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>34500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>34600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>26400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>35100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>37700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>34600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>31400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>36000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>38300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>34800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>24700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>12300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>27200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>26200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>22000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>19000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>24200</v>
       </c>
-      <c r="AQ35" s="3">
+      <c r="AR35" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AQ38" s="2">
+      <c r="AR38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4261,8 +4346,9 @@
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
       <c r="AQ39" s="3"/>
+      <c r="AR39" s="3"/>
     </row>
-    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4306,258 +4392,265 @@
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
+      <c r="AR40" s="3"/>
     </row>
-    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>268900</v>
+      </c>
+      <c r="E41" s="3">
         <v>215400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>253500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>275500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>273400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>226800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>211600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>234500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>239300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>174500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>189000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>186500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>209200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>202400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>55400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>97300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>72600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>75000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>17400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>75400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>117800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>141500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>41500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>114600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>115700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>108900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>97600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>124400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>110600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>104100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>665000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>688600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>440100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>479500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>500400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>647700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>468500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>420200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>131000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>147900</v>
       </c>
-      <c r="AQ41" s="3">
+      <c r="AR41" s="3">
         <v>188200</v>
       </c>
     </row>
-    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E42" s="3">
         <v>9500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1107000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1351400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2387500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2902400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3292400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3201700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3019400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1983400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1852900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1736800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2591900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>834800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>377100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>727300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>888700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>837700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>64900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>67300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>64100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>51000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>34100</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>34600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>34700</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>41700</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>41500</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>31800</v>
       </c>
-      <c r="AQ42" s="3">
+      <c r="AR42" s="3">
         <v>61800</v>
       </c>
     </row>
-    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4600,8 +4693,8 @@
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4681,53 +4774,56 @@
       <c r="AQ43" s="3">
         <v>0</v>
       </c>
+      <c r="AR43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E44" s="3">
         <v>2000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>400</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
         <v>600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>600</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4806,53 +4902,56 @@
       <c r="AQ44" s="3">
         <v>0</v>
       </c>
+      <c r="AR44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E45" s="3">
         <v>118600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>56400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>48200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>49100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>50300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>50200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>85200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>85700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>43100</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4931,53 +5030,56 @@
       <c r="AQ45" s="3">
         <v>0</v>
       </c>
+      <c r="AR45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2149400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1869300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1572000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1489700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1373600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1504900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1594400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1574000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1554500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1305500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1331400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1493700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1955500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1446000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -5056,383 +5158,395 @@
       <c r="AQ46" s="3">
         <v>0</v>
       </c>
+      <c r="AR46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3451700</v>
+      </c>
+      <c r="E47" s="3">
         <v>3371900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3229700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3213200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3117200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3029000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2910500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2888300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2769900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2813400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2890100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2769100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2821700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2854500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>163400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>139100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>102400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>102200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>96800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>92700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>92400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>92300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>77600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>66100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>59400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>54600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>51700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>32300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>33000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>26400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>27400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>21400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>22800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>18800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>19800</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>13500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>14900</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>15000</v>
       </c>
-      <c r="AQ47" s="3">
+      <c r="AR47" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>495400</v>
+      </c>
+      <c r="E48" s="3">
         <v>491100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>476800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>468900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>439900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>421100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>417200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>415800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>415700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>417000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>413100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>335500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>405100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>402800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>354300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>346600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>341900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>331900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>323500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>325800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>322100</v>
-      </c>
-      <c r="X48" s="3">
-        <v>320600</v>
       </c>
       <c r="Y48" s="3">
         <v>320600</v>
       </c>
       <c r="Z48" s="3">
+        <v>320600</v>
+      </c>
+      <c r="AA48" s="3">
         <v>315400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>304200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>285000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>279300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>280700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>271600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>269400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>211800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>210700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>208000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>207100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>194900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>197000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>199900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>198700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>198600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>203000</v>
       </c>
-      <c r="AQ48" s="3">
+      <c r="AR48" s="3">
         <v>202300</v>
       </c>
     </row>
-    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>910700</v>
+      </c>
+      <c r="E49" s="3">
         <v>906800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>690600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>693600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>573900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>514800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>517800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>520900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>523100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>526400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>521000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>524200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>527800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>550500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>501600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>503300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>502000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>504700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>507600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>508000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>494600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>497100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>497900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>492500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>495400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>498200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>501200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>503800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>501300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>504200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>492400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>485300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>486300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>474300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>308800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>310700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>308300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>302000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>302800</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>304300</v>
       </c>
-      <c r="AQ49" s="3">
+      <c r="AR49" s="3">
         <v>299000</v>
       </c>
     </row>
-    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5556,8 +5670,11 @@
       <c r="AQ50" s="3">
         <v>0</v>
       </c>
+      <c r="AR50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5681,53 +5798,56 @@
       <c r="AQ51" s="3">
         <v>0</v>
       </c>
+      <c r="AR51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>640000</v>
+      </c>
+      <c r="E52" s="3">
         <v>657700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>529800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>587300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>534500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>515500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>463200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>499700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>479500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>495500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>477000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>510100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>430500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>422900</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5806,8 +5926,11 @@
       <c r="AQ52" s="3">
         <v>0</v>
       </c>
+      <c r="AR52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5931,133 +6054,139 @@
       <c r="AQ53" s="3">
         <v>0</v>
       </c>
+      <c r="AR53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22617000</v>
+      </c>
+      <c r="E54" s="3">
         <v>22358700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19687300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19682500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18264600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17511900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17238300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17188000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17068800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16884200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16835000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16680400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17225100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16730500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15845300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15951800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16864000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16666600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16361400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15811400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15803800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15079400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>14626400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>14795400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15580300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12623800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11947700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12021300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11942500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11568300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11163000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11121200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>10831700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>10620400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>8522200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>8614800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>8427000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>8174800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>7973900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>7830100</v>
       </c>
-      <c r="AQ54" s="3">
+      <c r="AR54" s="3">
         <v>7940700</v>
       </c>
     </row>
-    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -6101,8 +6230,9 @@
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
       <c r="AQ55" s="3"/>
+      <c r="AR55" s="3"/>
     </row>
-    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6146,53 +6276,54 @@
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
       <c r="AQ56" s="3"/>
+      <c r="AR56" s="3"/>
     </row>
-    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18713400</v>
+      </c>
+      <c r="E57" s="3">
         <v>18480300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16509100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16530900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15328700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14608500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14437300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14363200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14272600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14126100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13893200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13880800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13766700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13598100</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6271,53 +6402,56 @@
       <c r="AQ57" s="3">
         <v>0</v>
       </c>
+      <c r="AR57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>155600</v>
+      </c>
+      <c r="E58" s="3">
         <v>191300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>52800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>42500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>34300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>33800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>38000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>31800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>41800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>39500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>35500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>150400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>805600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>556100</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6396,17 +6530,20 @@
       <c r="AQ58" s="3">
         <v>0</v>
       </c>
+      <c r="AR58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3">
         <v>52500</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6440,57 +6577,57 @@
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>53300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>55100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>56000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>57900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>56600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>58900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>60300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>62700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>64200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>62300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>49700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>51100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>50200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>52300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>43900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>44200</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6500,8 +6637,8 @@
       <c r="AJ59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK59" s="3">
-        <v>0</v>
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL59" s="3">
         <v>0</v>
@@ -6521,53 +6658,56 @@
       <c r="AQ59" s="3">
         <v>0</v>
       </c>
+      <c r="AR59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18869000</v>
+      </c>
+      <c r="E60" s="3">
         <v>18724100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16562000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16573400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15363100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14642400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14475300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14395000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14314400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14165600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13928700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14031200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14572200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14154200</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6646,119 +6786,122 @@
       <c r="AQ60" s="3">
         <v>0</v>
       </c>
+      <c r="AR60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>355400</v>
+      </c>
+      <c r="E61" s="3">
         <v>384500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>376000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>379800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>320200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>308000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>315800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>311600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>339100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>334800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>542500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>340900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>338400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>336600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>247400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>247300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>497100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>496800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>249700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>249500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>249400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>432400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>431900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>248900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1360200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>248600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>248500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>248300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>248200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>248000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>247900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>247700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>247600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>257700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>247200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>247100</v>
       </c>
-      <c r="AM61" s="3">
-        <v>0</v>
-      </c>
       <c r="AN61" s="3">
         <v>0</v>
       </c>
@@ -6771,53 +6914,56 @@
       <c r="AQ61" s="3">
         <v>0</v>
       </c>
+      <c r="AR61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>391000</v>
+      </c>
+      <c r="E62" s="3">
         <v>351600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>263000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>324200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>342400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>344500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>246500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>318700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>326000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>318000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>260400</v>
-      </c>
-      <c r="N62" s="3">
-        <v>324000</v>
       </c>
       <c r="O62" s="3">
         <v>324000</v>
       </c>
       <c r="P62" s="3">
+        <v>324000</v>
+      </c>
+      <c r="Q62" s="3">
         <v>249800</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6896,8 +7042,11 @@
       <c r="AQ62" s="3">
         <v>0</v>
       </c>
+      <c r="AR62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -7021,8 +7170,11 @@
       <c r="AQ63" s="3">
         <v>0</v>
       </c>
+      <c r="AR63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -7146,8 +7298,11 @@
       <c r="AQ64" s="3">
         <v>0</v>
       </c>
+      <c r="AR64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7271,133 +7426,139 @@
       <c r="AQ65" s="3">
         <v>0</v>
       </c>
+      <c r="AR65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19615400</v>
+      </c>
+      <c r="E66" s="3">
         <v>19460200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17258300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17277500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16025700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15294900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15091300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15025300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14979500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14818400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14779200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14696100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15234600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14740600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13971300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14125100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15010300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14804100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14462100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13928300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13950000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13279200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>12859600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13063700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13872700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10970600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10306900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10395900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10348700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10014400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9637500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9635300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9368900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>9181900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7390900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>7485200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>7316400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>7085000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>6898800</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>6762900</v>
       </c>
-      <c r="AQ66" s="3">
+      <c r="AR66" s="3">
         <v>6890400</v>
       </c>
     </row>
-    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7441,8 +7602,9 @@
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
       <c r="AQ67" s="3"/>
+      <c r="AR67" s="3"/>
     </row>
-    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7566,8 +7728,11 @@
       <c r="AQ68" s="3">
         <v>0</v>
       </c>
+      <c r="AR68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7691,8 +7856,11 @@
       <c r="AQ69" s="3">
         <v>0</v>
       </c>
+      <c r="AR69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7816,8 +7984,11 @@
       <c r="AQ70" s="3">
         <v>0</v>
       </c>
+      <c r="AR70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7941,133 +8112,139 @@
       <c r="AQ71" s="3">
         <v>0</v>
       </c>
+      <c r="AR71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1206000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1103400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1087300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1075700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1058000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1039500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1000100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>985300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>961200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>937100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>921100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>911000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>884900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>861900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>840800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>810800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>777400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>747600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>716600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>691000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>655100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>613800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>557900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>520900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>499500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>478000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>467200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>445200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>420600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>399000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>379200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>354800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>328100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>304900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>282700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>279200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>260800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>243300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>229500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>218600</v>
       </c>
-      <c r="AQ72" s="3">
+      <c r="AR72" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8191,8 +8368,11 @@
       <c r="AQ73" s="3">
         <v>0</v>
       </c>
+      <c r="AR73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8316,8 +8496,11 @@
       <c r="AQ74" s="3">
         <v>0</v>
       </c>
+      <c r="AR74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8441,133 +8624,139 @@
       <c r="AQ75" s="3">
         <v>0</v>
       </c>
+      <c r="AR75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2994500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2891700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2422100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2397500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2231300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2200700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2131600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2146300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2072800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2049500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2040000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1968000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1973800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1974700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1874000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1826700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1853700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1862500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1899300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1883100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1853800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1800200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1766800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1731700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1707600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1653200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1640800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1625400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1593800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1553800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1525500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1486000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1462800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1438500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1131200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1129600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1110700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1089800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1075100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1067200</v>
       </c>
-      <c r="AQ76" s="3">
+      <c r="AR76" s="3">
         <v>1050400</v>
       </c>
     </row>
-    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8691,263 +8880,272 @@
       <c r="AQ77" s="3">
         <v>0</v>
       </c>
+      <c r="AR77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AQ80" s="2">
+      <c r="AR80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>193200</v>
+      </c>
+      <c r="E81" s="3">
         <v>41000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>41100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>39000</v>
       </c>
-      <c r="G81" s="3">
-        <v>38800</v>
-      </c>
       <c r="H81" s="3">
+        <v>40900</v>
+      </c>
+      <c r="I81" s="3">
         <v>43700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>40900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>42900</v>
       </c>
       <c r="K81" s="3">
         <v>42900</v>
       </c>
       <c r="L81" s="3">
+        <v>42900</v>
+      </c>
+      <c r="M81" s="3">
         <v>34700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>44900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>41700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>38300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>46700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>50200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>46500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>45600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>40200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>50400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>55800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>69000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>50100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>34500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>34600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>26400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>35100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>37700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>34600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>31400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>36000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>38300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>34800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>24700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>12300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>27200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>26200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>22000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>19000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>24200</v>
       </c>
-      <c r="AQ81" s="3">
+      <c r="AR81" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8991,13 +9189,14 @@
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
       <c r="AQ82" s="3"/>
+      <c r="AR82" s="3"/>
     </row>
-    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="E83" s="3">
         <v>5600</v>
@@ -9006,70 +9205,70 @@
         <v>5600</v>
       </c>
       <c r="G83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H83" s="3">
         <v>5700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>5000</v>
       </c>
       <c r="K83" s="3">
         <v>5000</v>
       </c>
       <c r="L83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="M83" s="3">
         <v>4900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7200</v>
-      </c>
-      <c r="R83" s="3">
-        <v>7100</v>
       </c>
       <c r="S83" s="3">
         <v>7100</v>
       </c>
       <c r="T83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="U83" s="3">
         <v>7300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>7200</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>7300</v>
       </c>
       <c r="Z83" s="3">
         <v>7300</v>
       </c>
       <c r="AA83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AB83" s="3">
         <v>7200</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>7300</v>
       </c>
       <c r="AC83" s="3">
         <v>7300</v>
@@ -9078,7 +9277,7 @@
         <v>7300</v>
       </c>
       <c r="AE83" s="3">
-        <v>7400</v>
+        <v>7300</v>
       </c>
       <c r="AF83" s="3">
         <v>7400</v>
@@ -9087,37 +9286,40 @@
         <v>7400</v>
       </c>
       <c r="AH83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AI83" s="3">
         <v>7300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>6800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>6000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>6200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>6300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>5900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>6000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>5900</v>
       </c>
-      <c r="AQ83" s="3">
+      <c r="AR83" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9241,8 +9443,11 @@
       <c r="AQ84" s="3">
         <v>0</v>
       </c>
+      <c r="AR84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9366,8 +9571,11 @@
       <c r="AQ85" s="3">
         <v>0</v>
       </c>
+      <c r="AR85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9491,8 +9699,11 @@
       <c r="AQ86" s="3">
         <v>0</v>
       </c>
+      <c r="AR86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9616,8 +9827,11 @@
       <c r="AQ87" s="3">
         <v>0</v>
       </c>
+      <c r="AR87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9741,133 +9955,139 @@
       <c r="AQ88" s="3">
         <v>0</v>
       </c>
+      <c r="AR88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="E89" s="3">
         <v>40400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>117400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>52800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>121900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>100000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>25300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>38400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>43200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>104400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>34500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-20800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>78100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>86500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>90400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>160500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>111500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>240900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>93700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>72800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>202700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>14100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-91900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>51800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-104100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>42600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>188200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>74400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-40800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>85500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>21100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>107700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-161900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>157900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>115100</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>65300</v>
       </c>
-      <c r="AQ89" s="3">
+      <c r="AR89" s="3">
         <v>-38200</v>
       </c>
     </row>
-    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9911,133 +10131,137 @@
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
       <c r="AQ90" s="3"/>
+      <c r="AR90" s="3"/>
     </row>
-    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-14200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-7100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AQ91" s="3">
+      <c r="AR91" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -10161,8 +10385,11 @@
       <c r="AQ92" s="3">
         <v>0</v>
       </c>
+      <c r="AR92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10286,133 +10513,139 @@
       <c r="AQ93" s="3">
         <v>0</v>
       </c>
+      <c r="AR93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>202700</v>
+      </c>
+      <c r="E94" s="3">
         <v>166800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>19400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>111700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-234800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-283200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-121100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-46400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>43300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-77900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-209300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>32700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-42900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-116200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-223800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-215800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-788400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-819200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-616100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-28400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>275800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-178600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>83500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1009700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-194400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-370300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-109400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-158900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-114700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-173200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-113700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-140300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-209400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-77100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-95400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-19500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-17400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-273800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>900</v>
       </c>
-      <c r="AQ94" s="3">
+      <c r="AR94" s="3">
         <v>-93900</v>
       </c>
     </row>
-    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10456,22 +10689,23 @@
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
       <c r="AQ95" s="3"/>
+      <c r="AR95" s="3"/>
     </row>
-    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>21300</v>
+        <v>89400</v>
       </c>
       <c r="E96" s="3">
         <v>21300</v>
       </c>
       <c r="F96" s="3">
+        <v>21300</v>
+      </c>
+      <c r="G96" s="3">
         <v>20400</v>
-      </c>
-      <c r="G96" s="3">
-        <v>18800</v>
       </c>
       <c r="H96" s="3">
         <v>18800</v>
@@ -10480,88 +10714,88 @@
         <v>18800</v>
       </c>
       <c r="J96" s="3">
-        <v>18700</v>
+        <v>18800</v>
       </c>
       <c r="K96" s="3">
         <v>18700</v>
       </c>
       <c r="L96" s="3">
+        <v>18700</v>
+      </c>
+      <c r="M96" s="3">
         <v>18800</v>
-      </c>
-      <c r="M96" s="3">
-        <v>18700</v>
       </c>
       <c r="N96" s="3">
         <v>18700</v>
       </c>
       <c r="O96" s="3">
+        <v>18700</v>
+      </c>
+      <c r="P96" s="3">
         <v>17200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>16800</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-16700</v>
       </c>
       <c r="R96" s="3">
         <v>-16700</v>
       </c>
       <c r="S96" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="T96" s="3">
         <v>-14500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-14800</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-14500</v>
       </c>
       <c r="V96" s="3">
         <v>-14500</v>
       </c>
       <c r="W96" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="X96" s="3">
         <v>-13100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-13000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-13100</v>
       </c>
       <c r="AA96" s="3">
         <v>-13100</v>
       </c>
       <c r="AB96" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-13200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-11500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-11600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-11700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-11500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-11600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-10100</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-8800</v>
       </c>
       <c r="AL96" s="3">
         <v>-8800</v>
@@ -10570,7 +10804,7 @@
         <v>-8800</v>
       </c>
       <c r="AN96" s="3">
-        <v>-8100</v>
+        <v>-8800</v>
       </c>
       <c r="AO96" s="3">
         <v>-8100</v>
@@ -10581,8 +10815,11 @@
       <c r="AQ96" s="3">
         <v>-8100</v>
       </c>
+      <c r="AR96" s="3">
+        <v>-8100</v>
+      </c>
     </row>
-    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10706,8 +10943,11 @@
       <c r="AQ97" s="3">
         <v>0</v>
       </c>
+      <c r="AR97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10831,8 +11071,11 @@
       <c r="AQ98" s="3">
         <v>0</v>
       </c>
+      <c r="AR98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10956,133 +11199,139 @@
       <c r="AQ99" s="3">
         <v>0</v>
       </c>
+      <c r="AR99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E100" s="3">
         <v>4100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-36100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-26300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>59800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>139200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>64500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>67000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>131800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>78700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-557700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>402100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>226800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-140700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-881100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>180600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>329000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>537300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-68900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>642800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>349600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-231600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-875500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2878200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>641700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-81800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>329300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>285700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-37800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>291000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>142200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>99400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-107800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>182900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>229400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>148500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>140400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-133400</v>
       </c>
-      <c r="AQ100" s="3">
+      <c r="AR100" s="3">
         <v>157800</v>
       </c>
     </row>
-    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -11125,8 +11374,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -11206,129 +11455,135 @@
       <c r="AQ101" s="3">
         <v>0</v>
       </c>
+      <c r="AR101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>253500</v>
+      </c>
+      <c r="E102" s="3">
         <v>211300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>138300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-205600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-22100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>43400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>200300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-27200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-87400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-420500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>393700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>89700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-286400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1010400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-517400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-329600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>32700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>143700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1012200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>243700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>54600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-841600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1765100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>443500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-378800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-145200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>66300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>213600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-22800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>251700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-38900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-24500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-163800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>195100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>48000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>289000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-67200</v>
       </c>
-      <c r="AQ102" s="3">
+      <c r="AR102" s="3">
         <v>25800</v>
       </c>
     </row>
